--- a/output/yearly_benthic_cover_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_78_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30461896560793</v>
+        <v>45.35754253739683</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0626679844742</v>
+        <v>100.3865497896311</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03567789902186</v>
+        <v>87.96463863514255</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93864188120138</v>
+        <v>45.88671274544679</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228744529780954</v>
+        <v>2.228601599305443</v>
       </c>
       <c r="E3" t="n">
-        <v>5.71246571444642</v>
+        <v>5.678998276605372</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429148432603179</v>
+        <v>0.7428671997684813</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97649857846805</v>
+        <v>33.95920017905912</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17408278997462</v>
+        <v>34.17189118935013</v>
       </c>
       <c r="I3" t="n">
-        <v>6.557753672714504</v>
+        <v>6.540160192500998</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643217770376987</v>
+        <v>4.642919998553007</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96432210097815</v>
+        <v>12.03536136485745</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8616477591811</v>
+        <v>48.84315408680235</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646117413606</v>
+        <v>106.7652281971066</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16405079887122</v>
+        <v>86.91282043048389</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69979568701546</v>
+        <v>42.46620463237154</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186970975859942</v>
+        <v>2.177163372204886</v>
       </c>
       <c r="E4" t="n">
-        <v>6.518103010565651</v>
+        <v>6.458179905835617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444706755808016</v>
+        <v>0.7444232441035286</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33967408986043</v>
+        <v>33.17538980599461</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24565107671687</v>
+        <v>34.24346922876232</v>
       </c>
       <c r="I4" t="n">
-        <v>5.47623924790751</v>
+        <v>5.461549597935868</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65294172238001</v>
+        <v>4.652645275647053</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83594920112878</v>
+        <v>13.08717956951612</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28209528761369</v>
+        <v>44.26494468165397</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81784017575794</v>
+        <v>99.81832888354164</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.93335136084518</v>
+        <v>85.54151224043417</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31910809827241</v>
+        <v>41.94239669335779</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12672043656256</v>
+        <v>2.109498020181244</v>
       </c>
       <c r="E5" t="n">
-        <v>7.100468349210955</v>
+        <v>7.017358548897334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457908618788891</v>
+        <v>0.7457458403845753</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42117386005139</v>
+        <v>32.1443121852689</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30637964642889</v>
+        <v>34.30430865769046</v>
       </c>
       <c r="I5" t="n">
-        <v>4.571625319969446</v>
+        <v>4.559377485608052</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661192886743057</v>
+        <v>4.660911502403595</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0666486391548</v>
+        <v>14.45848775956584</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46212550568647</v>
+        <v>43.44740583602259</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84788224311369</v>
+        <v>99.84829028894622</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.54347075093922</v>
+        <v>83.93732423177109</v>
       </c>
       <c r="C6" t="n">
-        <v>41.63922085890468</v>
+        <v>41.04597345907013</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058840466089574</v>
+        <v>2.030566806884286</v>
       </c>
       <c r="E6" t="n">
-        <v>7.509741039685763</v>
+        <v>7.388993420840698</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469127716781659</v>
+        <v>0.7468727641858257</v>
       </c>
       <c r="G6" t="n">
-        <v>31.38636538852661</v>
+        <v>30.94156653814975</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35798749719563</v>
+        <v>34.35614715254798</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815418764774933</v>
+        <v>3.805222773001134</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668204822988537</v>
+        <v>4.667954776161411</v>
       </c>
       <c r="K6" t="n">
-        <v>15.45652924906079</v>
+        <v>16.0626757682289</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77726029981316</v>
+        <v>42.76470139810077</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87301040777862</v>
+        <v>99.87335062539979</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.01410782497496</v>
+        <v>82.17639984733715</v>
       </c>
       <c r="C7" t="n">
-        <v>40.70241601290125</v>
+        <v>39.87557830854342</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984491668514463</v>
+        <v>1.944475877102865</v>
       </c>
       <c r="E7" t="n">
-        <v>7.769146135247729</v>
+        <v>7.604902501992882</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478675718929625</v>
+        <v>0.7478346778089467</v>
       </c>
       <c r="G7" t="n">
-        <v>30.2529417137325</v>
+        <v>29.62972187333404</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40190830707627</v>
+        <v>34.40039517921155</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183580104180019</v>
+        <v>3.175103001580949</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674172324331015</v>
+        <v>4.673966736305918</v>
       </c>
       <c r="K7" t="n">
-        <v>16.98589217502505</v>
+        <v>17.82360015266286</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20570795749661</v>
+        <v>42.19512090621033</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89401614542291</v>
+        <v>99.89429936741661</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.9774619718782</v>
+        <v>87.03982867097909</v>
       </c>
       <c r="C8" t="n">
-        <v>43.05091484310632</v>
+        <v>42.15320643667921</v>
       </c>
       <c r="D8" t="n">
-        <v>1.988757849548446</v>
+        <v>1.948673509636958</v>
       </c>
       <c r="E8" t="n">
-        <v>9.635335072402921</v>
+        <v>9.421866237734152</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494753077689861</v>
+        <v>0.7494490640868422</v>
       </c>
       <c r="G8" t="n">
-        <v>30.76989575295316</v>
+        <v>30.12421575630558</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47586415737335</v>
+        <v>34.47465694799474</v>
       </c>
       <c r="I8" t="n">
-        <v>5.673913158275171</v>
+        <v>5.636910504678062</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684220673556163</v>
+        <v>4.684056650542765</v>
       </c>
       <c r="K8" t="n">
-        <v>12.0225380281218</v>
+        <v>12.96017132902091</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73782240305044</v>
+        <v>44.69912996595207</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81127527427856</v>
+        <v>99.81250773165218</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.99958867770184</v>
+        <v>84.86918508250866</v>
       </c>
       <c r="C9" t="n">
-        <v>41.95363418270205</v>
+        <v>40.85646521605394</v>
       </c>
       <c r="D9" t="n">
-        <v>1.899454277264029</v>
+        <v>1.850149377323957</v>
       </c>
       <c r="E9" t="n">
-        <v>9.992158465710467</v>
+        <v>9.72985188949494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508513690865372</v>
+        <v>0.75083432865947</v>
       </c>
       <c r="G9" t="n">
-        <v>29.38819832298111</v>
+        <v>28.60114777989913</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5391629779807</v>
+        <v>34.53837911833561</v>
       </c>
       <c r="I9" t="n">
-        <v>4.736942207888132</v>
+        <v>4.706108034673855</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692821056790857</v>
+        <v>4.692714554121688</v>
       </c>
       <c r="K9" t="n">
-        <v>14.00041132229816</v>
+        <v>15.13081491749135</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88834579615882</v>
+        <v>43.85613901910256</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84239130115904</v>
+        <v>99.84341915264785</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.77072705413141</v>
+        <v>82.45816973477949</v>
       </c>
       <c r="C10" t="n">
-        <v>40.45970945145618</v>
+        <v>39.17459414357526</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7997220546932</v>
+        <v>1.741895190439497</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12645661508425</v>
+        <v>9.815212005998786</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520326140673175</v>
+        <v>0.752026555452996</v>
       </c>
       <c r="G10" t="n">
-        <v>27.84514968465066</v>
+        <v>26.92766452777731</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59350024709659</v>
+        <v>34.59322155083781</v>
       </c>
       <c r="I10" t="n">
-        <v>3.953662000618655</v>
+        <v>3.927983932691855</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700203837920734</v>
+        <v>4.700165971581225</v>
       </c>
       <c r="K10" t="n">
-        <v>16.22927294586859</v>
+        <v>17.54183026522051</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17943587467833</v>
+        <v>43.15285036801885</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8684182720031</v>
+        <v>99.86927477681462</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.48876320759335</v>
+        <v>79.88207367435348</v>
       </c>
       <c r="C11" t="n">
-        <v>38.7905168442655</v>
+        <v>37.20625554322758</v>
       </c>
       <c r="D11" t="n">
-        <v>1.698748641601083</v>
+        <v>1.6275191241485</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10817250616791</v>
+        <v>9.717026508810777</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530475104125945</v>
+        <v>0.7530551510361967</v>
       </c>
       <c r="G11" t="n">
-        <v>26.28289744998581</v>
+        <v>25.15954417243394</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64018547897934</v>
+        <v>34.64053694766504</v>
       </c>
       <c r="I11" t="n">
-        <v>3.29916468036789</v>
+        <v>3.277797076282791</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706546940078716</v>
+        <v>4.706594693976229</v>
       </c>
       <c r="K11" t="n">
-        <v>18.51123679240667</v>
+        <v>20.1179263256465</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5884224188662</v>
+        <v>42.56670746632892</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89017605553838</v>
+        <v>99.89088933520301</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.09574472223828</v>
+        <v>77.30158191667638</v>
       </c>
       <c r="C12" t="n">
-        <v>36.90806493953013</v>
+        <v>35.13190279268046</v>
       </c>
       <c r="D12" t="n">
-        <v>1.593870336361524</v>
+        <v>1.514252577680624</v>
       </c>
       <c r="E12" t="n">
-        <v>9.94285727138549</v>
+        <v>9.496560355145064</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539210331894727</v>
+        <v>0.7539431854606303</v>
       </c>
       <c r="G12" t="n">
-        <v>24.66022904935556</v>
+        <v>23.40857569726561</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68036752671573</v>
+        <v>34.68138653118899</v>
       </c>
       <c r="I12" t="n">
-        <v>2.752493047796302</v>
+        <v>2.734718660806517</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712006457434204</v>
+        <v>4.71214490912894</v>
       </c>
       <c r="K12" t="n">
-        <v>20.90425527776171</v>
+        <v>22.69841808332362</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09603631936463</v>
+        <v>42.07862920521026</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90835653665647</v>
+        <v>99.90895008121436</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.74238711702158</v>
+        <v>74.83109423431416</v>
       </c>
       <c r="C13" t="n">
-        <v>34.97981078615817</v>
+        <v>33.08266616941283</v>
       </c>
       <c r="D13" t="n">
-        <v>1.491730512706385</v>
+        <v>1.406993814999226</v>
       </c>
       <c r="E13" t="n">
-        <v>9.688362159458123</v>
+        <v>9.204100317648054</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546729108597382</v>
+        <v>0.7547093248187203</v>
       </c>
       <c r="G13" t="n">
-        <v>23.07993020764024</v>
+        <v>21.7504805403346</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71495389954794</v>
+        <v>34.71662894166113</v>
       </c>
       <c r="I13" t="n">
-        <v>2.296031733935793</v>
+        <v>2.281248014735429</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716705692873363</v>
+        <v>4.716933280117003</v>
       </c>
       <c r="K13" t="n">
-        <v>23.25761288297841</v>
+        <v>25.16890576568585</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68611819064686</v>
+        <v>41.67246365765669</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92354185978343</v>
+        <v>99.92403559275537</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.62293640169865</v>
+        <v>82.21759401550048</v>
       </c>
       <c r="C14" t="n">
-        <v>39.16054009600436</v>
+        <v>37.70281297761561</v>
       </c>
       <c r="D14" t="n">
-        <v>1.493584173959692</v>
+        <v>1.408669858371549</v>
       </c>
       <c r="E14" t="n">
-        <v>12.03567900089451</v>
+        <v>11.75590945220996</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556106860958586</v>
+        <v>0.7556083519135147</v>
       </c>
       <c r="G14" t="n">
-        <v>24.92432809134552</v>
+        <v>23.8275377725425</v>
       </c>
       <c r="H14" t="n">
-        <v>36.57380975164315</v>
+        <v>36.80913174787293</v>
       </c>
       <c r="I14" t="n">
-        <v>3.117357909660818</v>
+        <v>2.938184633130563</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722566788099115</v>
+        <v>4.722552199459468</v>
       </c>
       <c r="K14" t="n">
-        <v>16.37706359830134</v>
+        <v>17.78240598449952</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35861333865559</v>
+        <v>44.41695807907088</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89621703296129</v>
+        <v>99.90217704118601</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.88207031416584</v>
+        <v>81.36425891096916</v>
       </c>
       <c r="C15" t="n">
-        <v>38.89879878445872</v>
+        <v>37.30247152955211</v>
       </c>
       <c r="D15" t="n">
-        <v>1.466048016847087</v>
+        <v>1.377556448661243</v>
       </c>
       <c r="E15" t="n">
-        <v>12.24971096065519</v>
+        <v>11.9047466458814</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564009563675798</v>
+        <v>0.7563670614045568</v>
       </c>
       <c r="G15" t="n">
-        <v>24.467321923037</v>
+        <v>23.30125694052277</v>
       </c>
       <c r="H15" t="n">
-        <v>36.61456726359756</v>
+        <v>36.8460919502627</v>
       </c>
       <c r="I15" t="n">
-        <v>2.600515216364061</v>
+        <v>2.450945730457987</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727505977297373</v>
+        <v>4.72729413377848</v>
       </c>
       <c r="K15" t="n">
-        <v>17.11792968583415</v>
+        <v>18.63574108903085</v>
       </c>
       <c r="L15" t="n">
-        <v>43.89667825443877</v>
+        <v>43.98017114160787</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91340672473164</v>
+        <v>99.91838376019082</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.39342824119355</v>
+        <v>78.75209334184856</v>
       </c>
       <c r="C16" t="n">
-        <v>36.81202245287403</v>
+        <v>35.06817065657964</v>
       </c>
       <c r="D16" t="n">
-        <v>1.371728592249074</v>
+        <v>1.28030200747652</v>
       </c>
       <c r="E16" t="n">
-        <v>11.82312306385264</v>
+        <v>11.4049842259687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570812224602552</v>
+        <v>0.7570215126654687</v>
       </c>
       <c r="G16" t="n">
-        <v>22.89319631547451</v>
+        <v>21.65620586123342</v>
       </c>
       <c r="H16" t="n">
-        <v>36.64749642424673</v>
+        <v>36.87797325838279</v>
       </c>
       <c r="I16" t="n">
-        <v>2.169044982533754</v>
+        <v>2.044222021962465</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731757640376594</v>
+        <v>4.73138445415918</v>
       </c>
       <c r="K16" t="n">
-        <v>19.60657175880643</v>
+        <v>21.24790665815146</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50916925453166</v>
+        <v>43.61584085942284</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92776346621213</v>
+        <v>99.93191817415394</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.17516287972293</v>
+        <v>80.62780087062841</v>
       </c>
       <c r="C17" t="n">
-        <v>38.0909914485442</v>
+        <v>36.42453834030519</v>
       </c>
       <c r="D17" t="n">
-        <v>1.372949117766261</v>
+        <v>1.281378735267666</v>
       </c>
       <c r="E17" t="n">
-        <v>12.63992121127758</v>
+        <v>12.24766469482828</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577548520367016</v>
+        <v>0.757658164093352</v>
       </c>
       <c r="G17" t="n">
-        <v>23.35425856022522</v>
+        <v>22.16846960655165</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12079685835111</v>
+        <v>37.40303843640294</v>
       </c>
       <c r="I17" t="n">
-        <v>2.193514454836669</v>
+        <v>2.034227707901073</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735967825229384</v>
+        <v>4.73536352558345</v>
       </c>
       <c r="K17" t="n">
-        <v>17.82483712027707</v>
+        <v>19.37219912937159</v>
       </c>
       <c r="L17" t="n">
-        <v>44.0111192824313</v>
+        <v>44.13551191799688</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92694785125256</v>
+        <v>99.93224938767366</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.80293644952025</v>
+        <v>78.11030523262832</v>
       </c>
       <c r="C18" t="n">
-        <v>36.05731209649704</v>
+        <v>34.22020718883822</v>
       </c>
       <c r="D18" t="n">
-        <v>1.286770861407796</v>
+        <v>1.19187428753267</v>
       </c>
       <c r="E18" t="n">
-        <v>12.15141713039953</v>
+        <v>11.67490011059416</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758333853380856</v>
+        <v>0.7582066637080376</v>
       </c>
       <c r="G18" t="n">
-        <v>21.88834168448591</v>
+        <v>20.61999952924075</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14916090144408</v>
+        <v>37.43011601986037</v>
       </c>
       <c r="I18" t="n">
-        <v>1.829325434771715</v>
+        <v>1.696416973517101</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739586583630349</v>
+        <v>4.738791648175235</v>
       </c>
       <c r="K18" t="n">
-        <v>20.19706355047976</v>
+        <v>21.88969476737169</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68469339594439</v>
+        <v>43.83359171857062</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9390690429212</v>
+        <v>99.94349367478051</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.85742505303718</v>
+        <v>77.14951784186717</v>
       </c>
       <c r="C19" t="n">
-        <v>35.39342511024266</v>
+        <v>33.5103720734207</v>
       </c>
       <c r="D19" t="n">
-        <v>1.253138059000082</v>
+        <v>1.157999478538079</v>
       </c>
       <c r="E19" t="n">
-        <v>12.08804788340535</v>
+        <v>11.58036343242906</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588228279443061</v>
+        <v>0.7586730517654526</v>
       </c>
       <c r="G19" t="n">
-        <v>21.31623806216621</v>
+        <v>20.03394900962802</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17311472422719</v>
+        <v>37.45314003156445</v>
       </c>
       <c r="I19" t="n">
-        <v>1.525420821642129</v>
+        <v>1.423686264408022</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742642674651913</v>
+        <v>4.74170657353408</v>
       </c>
       <c r="K19" t="n">
-        <v>21.14257494696282</v>
+        <v>22.85048215813283</v>
       </c>
       <c r="L19" t="n">
-        <v>43.41318534738419</v>
+        <v>43.59171873294935</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94918540458967</v>
+        <v>99.95257296450289</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.3090730846926</v>
+        <v>74.5501248103788</v>
       </c>
       <c r="C20" t="n">
-        <v>33.07975886717722</v>
+        <v>31.12932614426225</v>
       </c>
       <c r="D20" t="n">
-        <v>1.161640155924991</v>
+        <v>1.066716596409788</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41742051195405</v>
+        <v>10.86534470315608</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592444201760447</v>
+        <v>0.7590757210658714</v>
       </c>
       <c r="G20" t="n">
-        <v>19.75983246891981</v>
+        <v>18.45471116029947</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19376763004411</v>
+        <v>37.47301846227963</v>
       </c>
       <c r="I20" t="n">
-        <v>1.271890271573322</v>
+        <v>1.187034910506257</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745277626100279</v>
+        <v>4.744223256661697</v>
       </c>
       <c r="K20" t="n">
-        <v>23.6909269153074</v>
+        <v>25.4498751896212</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18694141691421</v>
+        <v>43.38125182543855</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95762719939883</v>
+        <v>99.960453159322</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.22280709581003</v>
+        <v>80.7423021053747</v>
       </c>
       <c r="C21" t="n">
-        <v>36.68740290840647</v>
+        <v>35.02878304667797</v>
       </c>
       <c r="D21" t="n">
-        <v>1.162533990824701</v>
+        <v>1.067437826604118</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3803870986272</v>
+        <v>12.95195014712053</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598286279074169</v>
+        <v>0.7595889486013364</v>
       </c>
       <c r="G21" t="n">
-        <v>21.41288265688648</v>
+        <v>20.27348984324124</v>
       </c>
       <c r="H21" t="n">
-        <v>38.86023252273394</v>
+        <v>39.30465583469655</v>
       </c>
       <c r="I21" t="n">
-        <v>1.898013274408943</v>
+        <v>1.637748576352581</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748928924421356</v>
+        <v>4.747430928758353</v>
       </c>
       <c r="K21" t="n">
-        <v>17.77719290418997</v>
+        <v>19.25769789462529</v>
       </c>
       <c r="L21" t="n">
-        <v>45.47218572229677</v>
+        <v>45.65896432512194</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93678153489321</v>
+        <v>99.9454452664252</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_78_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35754253739683</v>
+        <v>45.46148462717707</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3865497896311</v>
+        <v>99.03274109954907</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96463863514255</v>
+        <v>88.04088116185437</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88671274544679</v>
+        <v>45.93807110399444</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228601599305443</v>
+        <v>2.228758307614604</v>
       </c>
       <c r="E3" t="n">
-        <v>5.678998276605372</v>
+        <v>5.712435943029192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428671997684813</v>
+        <v>0.7429194358715346</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95920017905912</v>
+        <v>33.97624365049217</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17189118935013</v>
+        <v>34.17429405009059</v>
       </c>
       <c r="I3" t="n">
-        <v>6.540160192500998</v>
+        <v>6.56298330055919</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642919998553007</v>
+        <v>4.643246474197092</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03536136485745</v>
+        <v>11.95911883814564</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84315408680235</v>
+        <v>48.86723553986444</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652281971066</v>
+        <v>106.7644254820045</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91282043048389</v>
+        <v>87.17997888502855</v>
       </c>
       <c r="C4" t="n">
-        <v>42.46620463237154</v>
+        <v>42.71098051859268</v>
       </c>
       <c r="D4" t="n">
-        <v>2.177163372204886</v>
+        <v>2.187558446184391</v>
       </c>
       <c r="E4" t="n">
-        <v>6.458179905835617</v>
+        <v>6.520273899997236</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444232441035286</v>
+        <v>0.7444762360704775</v>
       </c>
       <c r="G4" t="n">
-        <v>33.17538980599461</v>
+        <v>33.34817351586297</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24346922876232</v>
+        <v>34.24590685924196</v>
       </c>
       <c r="I4" t="n">
-        <v>5.461549597935868</v>
+        <v>5.48061345223103</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652645275647053</v>
+        <v>4.652976475440485</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08717956951612</v>
+        <v>12.82002111497146</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26494468165397</v>
+        <v>44.28669327475367</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81832888354164</v>
+        <v>99.8176949083178</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.54151224043417</v>
+        <v>86.12539291358898</v>
       </c>
       <c r="C5" t="n">
-        <v>41.94239669335779</v>
+        <v>42.50709243948536</v>
       </c>
       <c r="D5" t="n">
-        <v>2.109498020181244</v>
+        <v>2.136480315468937</v>
       </c>
       <c r="E5" t="n">
-        <v>7.017358548897334</v>
+        <v>7.130573776650815</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457458403845753</v>
+        <v>0.7457945372884872</v>
       </c>
       <c r="G5" t="n">
-        <v>32.1443121852689</v>
+        <v>32.56951438155003</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30430865769046</v>
+        <v>34.30654871527041</v>
       </c>
       <c r="I5" t="n">
-        <v>4.559377485608052</v>
+        <v>4.575265329307252</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660911502403595</v>
+        <v>4.661215858053046</v>
       </c>
       <c r="K5" t="n">
-        <v>14.45848775956584</v>
+        <v>13.87460708641103</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44740583602259</v>
+        <v>43.46606121154164</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84829028894622</v>
+        <v>99.84776073743802</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.93732423177109</v>
+        <v>84.8710789740276</v>
       </c>
       <c r="C6" t="n">
-        <v>41.04597345907013</v>
+        <v>41.96350258935622</v>
       </c>
       <c r="D6" t="n">
-        <v>2.030566806884286</v>
+        <v>2.075533918199825</v>
       </c>
       <c r="E6" t="n">
-        <v>7.388993420840698</v>
+        <v>7.563569666943284</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468727641858257</v>
+        <v>0.7469130066267073</v>
       </c>
       <c r="G6" t="n">
-        <v>30.94156653814975</v>
+        <v>31.64041873391504</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35614715254798</v>
+        <v>34.35799830482853</v>
       </c>
       <c r="I6" t="n">
-        <v>3.805222773001134</v>
+        <v>3.818439052097275</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667954776161411</v>
+        <v>4.668206291416921</v>
       </c>
       <c r="K6" t="n">
-        <v>16.0626757682289</v>
+        <v>15.12892102597241</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76470139810077</v>
+        <v>42.7804856810795</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87335062539979</v>
+        <v>99.87290929640814</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.17639984733715</v>
+        <v>83.49858284762723</v>
       </c>
       <c r="C7" t="n">
-        <v>39.87557830854342</v>
+        <v>41.18427795652026</v>
       </c>
       <c r="D7" t="n">
-        <v>1.944475877102865</v>
+        <v>2.009076946846772</v>
       </c>
       <c r="E7" t="n">
-        <v>7.604902501992882</v>
+        <v>7.852403387158126</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478346778089467</v>
+        <v>0.7478630125480797</v>
       </c>
       <c r="G7" t="n">
-        <v>29.62972187333404</v>
+        <v>30.62731729386623</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40039517921155</v>
+        <v>34.40169857721166</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175103001580949</v>
+        <v>3.186079801570866</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673966736305918</v>
+        <v>4.674143828425499</v>
       </c>
       <c r="K7" t="n">
-        <v>17.82360015266286</v>
+        <v>16.50141715237275</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19512090621033</v>
+        <v>42.20823713965985</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89429936741661</v>
+        <v>99.89393224855287</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.03982867097909</v>
+        <v>88.46626461932287</v>
       </c>
       <c r="C8" t="n">
-        <v>42.15320643667921</v>
+        <v>43.48044684324808</v>
       </c>
       <c r="D8" t="n">
-        <v>1.948673509636958</v>
+        <v>2.013415848134181</v>
       </c>
       <c r="E8" t="n">
-        <v>9.421866237734152</v>
+        <v>9.686876638717308</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494490640868422</v>
+        <v>0.7494781342551122</v>
       </c>
       <c r="G8" t="n">
-        <v>30.12421575630558</v>
+        <v>31.12457873149106</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47465694799474</v>
+        <v>34.47599417573516</v>
       </c>
       <c r="I8" t="n">
-        <v>5.636910504678062</v>
+        <v>5.731682751895592</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684056650542765</v>
+        <v>4.684238339094452</v>
       </c>
       <c r="K8" t="n">
-        <v>12.96017132902091</v>
+        <v>11.53373538067712</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69912996595207</v>
+        <v>44.79517340928648</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81250773165218</v>
+        <v>99.80935563321168</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.86918508250866</v>
+        <v>86.74261142968746</v>
       </c>
       <c r="C9" t="n">
-        <v>40.85646521605394</v>
+        <v>42.64676321183661</v>
       </c>
       <c r="D9" t="n">
-        <v>1.850149377323957</v>
+        <v>1.935931454147307</v>
       </c>
       <c r="E9" t="n">
-        <v>9.72985188949494</v>
+        <v>10.11161729674486</v>
       </c>
       <c r="F9" t="n">
-        <v>0.75083432865947</v>
+        <v>0.7508563080394102</v>
       </c>
       <c r="G9" t="n">
-        <v>28.60114777989913</v>
+        <v>29.92677892111348</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53837911833561</v>
+        <v>34.53939016981287</v>
       </c>
       <c r="I9" t="n">
-        <v>4.706108034673855</v>
+        <v>4.785185354583207</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692714554121688</v>
+        <v>4.692851925246314</v>
       </c>
       <c r="K9" t="n">
-        <v>15.13081491749135</v>
+        <v>13.25738857031256</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85613901910256</v>
+        <v>43.93663480807594</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84341915264785</v>
+        <v>99.84078659022511</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.45816973477949</v>
+        <v>84.72977780353352</v>
       </c>
       <c r="C10" t="n">
-        <v>39.17459414357526</v>
+        <v>41.37695943091656</v>
       </c>
       <c r="D10" t="n">
-        <v>1.741895190439497</v>
+        <v>1.845991891455177</v>
       </c>
       <c r="E10" t="n">
-        <v>9.815212005998786</v>
+        <v>10.30750480741201</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752026555452996</v>
+        <v>0.7520360821859454</v>
       </c>
       <c r="G10" t="n">
-        <v>26.92766452777731</v>
+        <v>28.53643971091942</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59322155083781</v>
+        <v>34.59365978055349</v>
       </c>
       <c r="I10" t="n">
-        <v>3.927983932691855</v>
+        <v>3.993920017345313</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700165971581225</v>
+        <v>4.70022551366216</v>
       </c>
       <c r="K10" t="n">
-        <v>17.54183026522051</v>
+        <v>15.27022219646649</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15285036801885</v>
+        <v>43.21989655721185</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86927477681462</v>
+        <v>99.86707818459492</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.88207367435348</v>
+        <v>82.64776983791236</v>
       </c>
       <c r="C11" t="n">
-        <v>37.20625554322758</v>
+        <v>39.91467563987158</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6275191241485</v>
+        <v>1.753891180869535</v>
       </c>
       <c r="E11" t="n">
-        <v>9.717026508810777</v>
+        <v>10.34869681064511</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530551510361967</v>
+        <v>0.7530469346371725</v>
       </c>
       <c r="G11" t="n">
-        <v>25.15954417243394</v>
+        <v>27.11269219224088</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64053694766504</v>
+        <v>34.64015899330994</v>
       </c>
       <c r="I11" t="n">
-        <v>3.277797076282791</v>
+        <v>3.332740384727402</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706594693976229</v>
+        <v>4.706543341482329</v>
       </c>
       <c r="K11" t="n">
-        <v>20.1179263256465</v>
+        <v>17.35223016208764</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56670746632892</v>
+        <v>42.62215197533674</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89088933520301</v>
+        <v>99.88905777729596</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.30158191667638</v>
+        <v>80.42961198485131</v>
       </c>
       <c r="C12" t="n">
-        <v>35.13190279268046</v>
+        <v>38.21304987432155</v>
       </c>
       <c r="D12" t="n">
-        <v>1.514252577680624</v>
+        <v>1.65659153300159</v>
       </c>
       <c r="E12" t="n">
-        <v>9.496560355145064</v>
+        <v>10.23800190776563</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539431854606303</v>
+        <v>0.753914705821305</v>
       </c>
       <c r="G12" t="n">
-        <v>23.40857569726561</v>
+        <v>25.6085764113809</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68138653118899</v>
+        <v>34.68007646778003</v>
       </c>
       <c r="I12" t="n">
-        <v>2.734718660806517</v>
+        <v>2.780484047718692</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71214490912894</v>
+        <v>4.711966911383158</v>
       </c>
       <c r="K12" t="n">
-        <v>22.69841808332362</v>
+        <v>19.5703880151487</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07862920521026</v>
+        <v>42.12398598873177</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90895008121436</v>
+        <v>99.90742387820201</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.83109423431416</v>
+        <v>78.15482017589923</v>
       </c>
       <c r="C13" t="n">
-        <v>33.08266616941283</v>
+        <v>36.3684710889783</v>
       </c>
       <c r="D13" t="n">
-        <v>1.406993814999226</v>
+        <v>1.557648667058006</v>
       </c>
       <c r="E13" t="n">
-        <v>9.204100317648054</v>
+        <v>10.01307944905824</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547093248187203</v>
+        <v>0.754660491007671</v>
       </c>
       <c r="G13" t="n">
-        <v>21.7504805403346</v>
+        <v>24.07905878896114</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71662894166113</v>
+        <v>34.71438258635287</v>
       </c>
       <c r="I13" t="n">
-        <v>2.281248014735429</v>
+        <v>2.319362124663359</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716933280117003</v>
+        <v>4.716628068797945</v>
       </c>
       <c r="K13" t="n">
-        <v>25.16890576568585</v>
+        <v>21.84517982410076</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67246365765669</v>
+        <v>41.70911341892877</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92403559275537</v>
+        <v>99.92276433200783</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.21759401550048</v>
+        <v>84.55324052624294</v>
       </c>
       <c r="C14" t="n">
-        <v>37.70281297761561</v>
+        <v>40.066264418812</v>
       </c>
       <c r="D14" t="n">
-        <v>1.408669858371549</v>
+        <v>1.559736104145342</v>
       </c>
       <c r="E14" t="n">
-        <v>11.75590945220996</v>
+        <v>12.14313918425499</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556083519135147</v>
+        <v>0.7556718270878743</v>
       </c>
       <c r="G14" t="n">
-        <v>23.8275377725425</v>
+        <v>25.66141093017792</v>
       </c>
       <c r="H14" t="n">
-        <v>36.80913174787293</v>
+        <v>36.31098734422191</v>
       </c>
       <c r="I14" t="n">
-        <v>2.938184633130563</v>
+        <v>3.399346217055711</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722552199459468</v>
+        <v>4.722948919299216</v>
       </c>
       <c r="K14" t="n">
-        <v>17.78240598449952</v>
+        <v>15.44675947375706</v>
       </c>
       <c r="L14" t="n">
-        <v>44.41695807907088</v>
+        <v>44.37381621476719</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90217704118601</v>
+        <v>99.88684010733624</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.36425891096916</v>
+        <v>83.99985879779015</v>
       </c>
       <c r="C15" t="n">
-        <v>37.30247152955211</v>
+        <v>40.03870773624883</v>
       </c>
       <c r="D15" t="n">
-        <v>1.377556448661243</v>
+        <v>1.539540024127676</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9047466458814</v>
+        <v>12.4585677657021</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563670614045568</v>
+        <v>0.7565222521470352</v>
       </c>
       <c r="G15" t="n">
-        <v>23.30125694052277</v>
+        <v>25.32913683128728</v>
       </c>
       <c r="H15" t="n">
-        <v>36.8460919502627</v>
+        <v>36.35185134424611</v>
       </c>
       <c r="I15" t="n">
-        <v>2.450945730457987</v>
+        <v>2.835976504360977</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72729413377848</v>
+        <v>4.728264075918971</v>
       </c>
       <c r="K15" t="n">
-        <v>18.63574108903085</v>
+        <v>16.00014120220986</v>
       </c>
       <c r="L15" t="n">
-        <v>43.98017114160787</v>
+        <v>43.86672477773422</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91838376019082</v>
+        <v>99.9055737161929</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.75209334184856</v>
+        <v>81.8082641276918</v>
       </c>
       <c r="C16" t="n">
-        <v>35.06817065657964</v>
+        <v>38.28605782877146</v>
       </c>
       <c r="D16" t="n">
-        <v>1.28030200747652</v>
+        <v>1.455147100728623</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4049842259687</v>
+        <v>12.16989207987958</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570215126654687</v>
+        <v>0.7572514461050546</v>
       </c>
       <c r="G16" t="n">
-        <v>21.65620586123342</v>
+        <v>23.94067023031135</v>
       </c>
       <c r="H16" t="n">
-        <v>36.87797325838279</v>
+        <v>36.3868900364826</v>
       </c>
       <c r="I16" t="n">
-        <v>2.044222021962465</v>
+        <v>2.365591696027994</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73138445415918</v>
+        <v>4.732821538156592</v>
       </c>
       <c r="K16" t="n">
-        <v>21.24790665815146</v>
+        <v>18.19173587230818</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61584085942284</v>
+        <v>43.44342917379922</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93191817415394</v>
+        <v>99.92122287487888</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.62780087062841</v>
+        <v>83.49922637348654</v>
       </c>
       <c r="C17" t="n">
-        <v>36.42453834030519</v>
+        <v>39.49383351829422</v>
       </c>
       <c r="D17" t="n">
-        <v>1.281378735267666</v>
+        <v>1.456555006744194</v>
       </c>
       <c r="E17" t="n">
-        <v>12.24766469482828</v>
+        <v>12.9696407375708</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757658164093352</v>
+        <v>0.7579841135211098</v>
       </c>
       <c r="G17" t="n">
-        <v>22.16846960655165</v>
+        <v>24.34786533387624</v>
       </c>
       <c r="H17" t="n">
-        <v>37.40303843640294</v>
+        <v>36.80612729559826</v>
       </c>
       <c r="I17" t="n">
-        <v>2.034227707901073</v>
+        <v>2.423653176668988</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73536352558345</v>
+        <v>4.737400709506937</v>
       </c>
       <c r="K17" t="n">
-        <v>19.37219912937159</v>
+        <v>16.50077362651348</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13551191799688</v>
+        <v>43.92468250607234</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93224938767366</v>
+        <v>99.91928965088005</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.11030523262832</v>
+        <v>81.41617372956972</v>
       </c>
       <c r="C18" t="n">
-        <v>34.22020718883822</v>
+        <v>37.78561104455513</v>
       </c>
       <c r="D18" t="n">
-        <v>1.19187428753267</v>
+        <v>1.379445411183325</v>
       </c>
       <c r="E18" t="n">
-        <v>11.67490011059416</v>
+        <v>12.61992883429252</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582066637080376</v>
+        <v>0.7586114154996043</v>
       </c>
       <c r="G18" t="n">
-        <v>20.61999952924075</v>
+        <v>23.05889647243768</v>
       </c>
       <c r="H18" t="n">
-        <v>37.43011601986037</v>
+        <v>36.83658777103751</v>
       </c>
       <c r="I18" t="n">
-        <v>1.696416973517101</v>
+        <v>2.021382478246545</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738791648175235</v>
+        <v>4.741321346872527</v>
       </c>
       <c r="K18" t="n">
-        <v>21.88969476737169</v>
+        <v>18.58382627043028</v>
       </c>
       <c r="L18" t="n">
-        <v>43.83359171857062</v>
+        <v>43.56323898566269</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94349367478051</v>
+        <v>99.9326763006481</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.14951784186717</v>
+        <v>80.59630640427616</v>
       </c>
       <c r="C19" t="n">
-        <v>33.5103720734207</v>
+        <v>37.2777623745427</v>
       </c>
       <c r="D19" t="n">
-        <v>1.157999478538079</v>
+        <v>1.349867347985541</v>
       </c>
       <c r="E19" t="n">
-        <v>11.58036343242906</v>
+        <v>12.6302756616714</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586730517654526</v>
+        <v>0.7591402903292142</v>
       </c>
       <c r="G19" t="n">
-        <v>20.03394900962802</v>
+        <v>22.56446770301805</v>
       </c>
       <c r="H19" t="n">
-        <v>37.45314003156445</v>
+        <v>36.8622688294592</v>
       </c>
       <c r="I19" t="n">
-        <v>1.423686264408022</v>
+        <v>1.685659757255161</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74170657353408</v>
+        <v>4.744626814557589</v>
       </c>
       <c r="K19" t="n">
-        <v>22.85048215813283</v>
+        <v>19.40369359572383</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59171873294935</v>
+        <v>43.26239451644882</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95257296450289</v>
+        <v>99.94385048671535</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.5501248103788</v>
+        <v>78.31408660359881</v>
       </c>
       <c r="C20" t="n">
-        <v>31.12932614426225</v>
+        <v>35.25565061305674</v>
       </c>
       <c r="D20" t="n">
-        <v>1.066716596409788</v>
+        <v>1.266324938674052</v>
       </c>
       <c r="E20" t="n">
-        <v>10.86534470315608</v>
+        <v>12.08285561699103</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590757210658714</v>
+        <v>0.7595944507821375</v>
       </c>
       <c r="G20" t="n">
-        <v>18.45471116029947</v>
+        <v>21.1679675213116</v>
       </c>
       <c r="H20" t="n">
-        <v>37.47301846227963</v>
+        <v>36.88432191361326</v>
       </c>
       <c r="I20" t="n">
-        <v>1.187034910506257</v>
+        <v>1.405556844838379</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744223256661697</v>
+        <v>4.747465317388359</v>
       </c>
       <c r="K20" t="n">
-        <v>25.4498751896212</v>
+        <v>21.68591339640118</v>
       </c>
       <c r="L20" t="n">
-        <v>43.38125182543855</v>
+        <v>43.01161210839609</v>
       </c>
       <c r="M20" t="n">
-        <v>99.960453159322</v>
+        <v>99.95317611785401</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.7423021053747</v>
+        <v>83.68882149013066</v>
       </c>
       <c r="C21" t="n">
-        <v>35.02878304667797</v>
+        <v>38.35502942308525</v>
       </c>
       <c r="D21" t="n">
-        <v>1.067437826604118</v>
+        <v>1.267474297239342</v>
       </c>
       <c r="E21" t="n">
-        <v>12.95195014712053</v>
+        <v>13.82425972696604</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595889486013364</v>
+        <v>0.7602838839295788</v>
       </c>
       <c r="G21" t="n">
-        <v>20.27348984324124</v>
+        <v>22.53782381331309</v>
       </c>
       <c r="H21" t="n">
-        <v>39.30465583469655</v>
+        <v>38.2684428907554</v>
       </c>
       <c r="I21" t="n">
-        <v>1.637748576352581</v>
+        <v>2.278762603367344</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747430928758353</v>
+        <v>4.751774274559867</v>
       </c>
       <c r="K21" t="n">
-        <v>19.25769789462529</v>
+        <v>16.31117850986934</v>
       </c>
       <c r="L21" t="n">
-        <v>45.65896432512194</v>
+        <v>45.25790219376891</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9454452664252</v>
+        <v>99.92411012672349</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_78_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_78_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.46148462717707</v>
+        <v>44.69093179347443</v>
       </c>
       <c r="M2" t="n">
-        <v>99.03274109954907</v>
+        <v>91.77375046592633</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04088116185437</v>
+        <v>81.4637154571119</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93807110399444</v>
+        <v>43.21927101266746</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228758307614604</v>
+        <v>2.178754846543961</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712435943029192</v>
+        <v>4.160964013591783</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429194358715346</v>
+        <v>0.7376236710631772</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97624365049217</v>
+        <v>32.77210415009874</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17429405009059</v>
+        <v>33.93068886890615</v>
       </c>
       <c r="I3" t="n">
-        <v>6.56298330055919</v>
+        <v>3.073431962763238</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643246474197092</v>
+        <v>4.610147944144857</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95911883814564</v>
+        <v>18.5362845428881</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86723553986444</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644254820045</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.17997888502855</v>
+        <v>88.46269299859924</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71098051859268</v>
+        <v>42.7583195808599</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187558446184391</v>
+        <v>2.184461085402825</v>
       </c>
       <c r="E4" t="n">
-        <v>6.520273899997236</v>
+        <v>6.502334356780361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444762360704775</v>
+        <v>0.7395555345134022</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34817351586297</v>
+        <v>33.44395421150186</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24590685924196</v>
+        <v>34.0195545876165</v>
       </c>
       <c r="I4" t="n">
-        <v>5.48061345223103</v>
+        <v>6.950611132075525</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652976475440485</v>
+        <v>4.622222090708763</v>
       </c>
       <c r="K4" t="n">
-        <v>12.82002111497146</v>
+        <v>11.53730700140077</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28669327475367</v>
+        <v>45.47329159178165</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8176949083178</v>
+        <v>99.76891817404231</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12539291358898</v>
+        <v>87.29984107632755</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50709243948536</v>
+        <v>42.67281592315949</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136480315468937</v>
+        <v>2.128875944882204</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130573776650815</v>
+        <v>7.30438029793955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457945372884872</v>
+        <v>0.7411947625731624</v>
       </c>
       <c r="G5" t="n">
-        <v>32.56951438155003</v>
+        <v>32.59294939991067</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30654871527041</v>
+        <v>34.09495907836547</v>
       </c>
       <c r="I5" t="n">
-        <v>4.575265329307252</v>
+        <v>5.805014326574256</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661215858053046</v>
+        <v>4.632467266082264</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87460708641103</v>
+        <v>12.70015892367244</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46606121154164</v>
+        <v>44.43395262172153</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84776073743802</v>
+        <v>99.80692746855345</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.8710789740276</v>
+        <v>85.89136328123439</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96350258935622</v>
+        <v>42.1651746000144</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075533918199825</v>
+        <v>2.061398231838747</v>
       </c>
       <c r="E6" t="n">
-        <v>7.563569666943284</v>
+        <v>7.880626180598879</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469130066267073</v>
+        <v>0.7425888812370887</v>
       </c>
       <c r="G6" t="n">
-        <v>31.64041873391504</v>
+        <v>31.55987009243191</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35799830482853</v>
+        <v>34.15908853690608</v>
       </c>
       <c r="I6" t="n">
-        <v>3.818439052097275</v>
+        <v>4.8466108504899</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668206291416921</v>
+        <v>4.641180507731804</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12892102597241</v>
+        <v>14.10863671876559</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7804856810795</v>
+        <v>43.56493828325961</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87290929640814</v>
+        <v>99.83874960203961</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.49858284762723</v>
+        <v>84.31352282942369</v>
       </c>
       <c r="C7" t="n">
-        <v>41.18427795652026</v>
+        <v>41.33978333019727</v>
       </c>
       <c r="D7" t="n">
-        <v>2.009076946846772</v>
+        <v>1.986198402779414</v>
       </c>
       <c r="E7" t="n">
-        <v>7.852403387158126</v>
+        <v>8.267357810617018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478630125480797</v>
+        <v>0.7437765104522048</v>
       </c>
       <c r="G7" t="n">
-        <v>30.62731729386623</v>
+        <v>30.40856570134942</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40169857721166</v>
+        <v>34.21371948080142</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186079801570866</v>
+        <v>4.045301733097922</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674143828425499</v>
+        <v>4.64860319032628</v>
       </c>
       <c r="K7" t="n">
-        <v>16.50141715237275</v>
+        <v>15.68647717057633</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20823713965985</v>
+        <v>42.83911142004613</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89393224855287</v>
+        <v>99.86537192081973</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.46626461932287</v>
+        <v>82.50910999896962</v>
       </c>
       <c r="C8" t="n">
-        <v>43.48044684324808</v>
+        <v>40.16333305767427</v>
       </c>
       <c r="D8" t="n">
-        <v>2.013415848134181</v>
+        <v>1.900647826096811</v>
       </c>
       <c r="E8" t="n">
-        <v>9.686876638717308</v>
+        <v>8.473875538738543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494781342551122</v>
+        <v>0.7447908441329221</v>
       </c>
       <c r="G8" t="n">
-        <v>31.12457873149106</v>
+        <v>29.09879205124434</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47599417573516</v>
+        <v>34.26037883011441</v>
       </c>
       <c r="I8" t="n">
-        <v>5.731682751895592</v>
+        <v>3.375682132811838</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684238339094452</v>
+        <v>4.654942775830762</v>
       </c>
       <c r="K8" t="n">
-        <v>11.53373538067712</v>
+        <v>17.49089000103038</v>
       </c>
       <c r="L8" t="n">
-        <v>44.79517340928648</v>
+        <v>42.2334074487093</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80935563321168</v>
+        <v>99.88763050741395</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.74261142968746</v>
+        <v>80.43818878990865</v>
       </c>
       <c r="C9" t="n">
-        <v>42.64676321183661</v>
+        <v>38.61602979181994</v>
       </c>
       <c r="D9" t="n">
-        <v>1.935931454147307</v>
+        <v>1.803034411935318</v>
       </c>
       <c r="E9" t="n">
-        <v>10.11161729674486</v>
+        <v>8.508066415852612</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508563080394102</v>
+        <v>0.74566008003221</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92677892111348</v>
+        <v>27.60433716007683</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53939016981287</v>
+        <v>34.30036368148166</v>
       </c>
       <c r="I9" t="n">
-        <v>4.785185354583207</v>
+        <v>2.816351540328716</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692851925246314</v>
+        <v>4.660375500201312</v>
       </c>
       <c r="K9" t="n">
-        <v>13.25738857031256</v>
+        <v>19.56181121009136</v>
       </c>
       <c r="L9" t="n">
-        <v>43.93663480807594</v>
+        <v>41.72839004995504</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84078659022511</v>
+        <v>99.90623105186634</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.72977780353352</v>
+        <v>85.37783005799392</v>
       </c>
       <c r="C10" t="n">
-        <v>41.37695943091656</v>
+        <v>42.03284195419302</v>
       </c>
       <c r="D10" t="n">
-        <v>1.845991891455177</v>
+        <v>1.805036109887026</v>
       </c>
       <c r="E10" t="n">
-        <v>10.30750480741201</v>
+        <v>10.44221800992726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520360821859454</v>
+        <v>0.7464878990937822</v>
       </c>
       <c r="G10" t="n">
-        <v>28.53643971091942</v>
+        <v>29.08576407718221</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59365978055349</v>
+        <v>35.78922441265279</v>
       </c>
       <c r="I10" t="n">
-        <v>3.993920017345313</v>
+        <v>2.843550179914726</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70022551366216</v>
+        <v>4.665549369336139</v>
       </c>
       <c r="K10" t="n">
-        <v>15.27022219646649</v>
+        <v>14.62216994200608</v>
       </c>
       <c r="L10" t="n">
-        <v>43.21989655721185</v>
+        <v>43.25030820980196</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86707818459492</v>
+        <v>99.90532010600107</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.64776983791236</v>
+        <v>84.83851677414297</v>
       </c>
       <c r="C11" t="n">
-        <v>39.91467563987158</v>
+        <v>41.82472653560794</v>
       </c>
       <c r="D11" t="n">
-        <v>1.753891180869535</v>
+        <v>1.773241361738175</v>
       </c>
       <c r="E11" t="n">
-        <v>10.34869681064511</v>
+        <v>10.71671929350232</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530469346371725</v>
+        <v>0.7471996039603397</v>
       </c>
       <c r="G11" t="n">
-        <v>27.11269219224088</v>
+        <v>28.62744215578031</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64015899330994</v>
+        <v>35.87735431412065</v>
       </c>
       <c r="I11" t="n">
-        <v>3.332740384727402</v>
+        <v>2.426562520289055</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706543341482329</v>
+        <v>4.669997524752123</v>
       </c>
       <c r="K11" t="n">
-        <v>17.35223016208764</v>
+        <v>15.16148322585702</v>
       </c>
       <c r="L11" t="n">
-        <v>42.62215197533674</v>
+        <v>42.93298186425373</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88905777729596</v>
+        <v>99.9191916257187</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.42961198485131</v>
+        <v>82.55094644847746</v>
       </c>
       <c r="C12" t="n">
-        <v>38.21304987432155</v>
+        <v>39.91405466157802</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65659153300159</v>
+        <v>1.675955373848594</v>
       </c>
       <c r="E12" t="n">
-        <v>10.23800190776563</v>
+        <v>10.46606199521855</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753914705821305</v>
+        <v>0.7478102060916632</v>
       </c>
       <c r="G12" t="n">
-        <v>25.6085764113809</v>
+        <v>27.05684435055713</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68007646778003</v>
+        <v>35.90667283743669</v>
       </c>
       <c r="I12" t="n">
-        <v>2.780484047718692</v>
+        <v>2.023787897251951</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711966911383158</v>
+        <v>4.673813788072895</v>
       </c>
       <c r="K12" t="n">
-        <v>19.5703880151487</v>
+        <v>17.44905355152251</v>
       </c>
       <c r="L12" t="n">
-        <v>42.12398598873177</v>
+        <v>42.56948727244699</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90742387820201</v>
+        <v>99.93259548554752</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.15482017589923</v>
+        <v>83.6021626202768</v>
       </c>
       <c r="C13" t="n">
-        <v>36.3684710889783</v>
+        <v>40.81710626974075</v>
       </c>
       <c r="D13" t="n">
-        <v>1.557648667058006</v>
+        <v>1.677200854772582</v>
       </c>
       <c r="E13" t="n">
-        <v>10.01307944905824</v>
+        <v>11.06470212370869</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754660491007671</v>
+        <v>0.7483659388760701</v>
       </c>
       <c r="G13" t="n">
-        <v>24.07905878896114</v>
+        <v>27.35717045553437</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71438258635287</v>
+        <v>36.21357566440365</v>
       </c>
       <c r="I13" t="n">
-        <v>2.319362124663359</v>
+        <v>1.863860465006003</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716628068797945</v>
+        <v>4.677287117975438</v>
       </c>
       <c r="K13" t="n">
-        <v>21.84517982410076</v>
+        <v>16.3978373797232</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70911341892877</v>
+        <v>42.72297380481626</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92276433200783</v>
+        <v>99.93791745428021</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.55324052624294</v>
+        <v>81.33529735369387</v>
       </c>
       <c r="C14" t="n">
-        <v>40.066264418812</v>
+        <v>38.83944361533739</v>
       </c>
       <c r="D14" t="n">
-        <v>1.559736104145342</v>
+        <v>1.583393894360601</v>
       </c>
       <c r="E14" t="n">
-        <v>12.14313918425499</v>
+        <v>10.70488036466473</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556718270878743</v>
+        <v>0.7488426138895129</v>
       </c>
       <c r="G14" t="n">
-        <v>25.66141093017792</v>
+        <v>25.82706569878829</v>
       </c>
       <c r="H14" t="n">
-        <v>36.31098734422191</v>
+        <v>36.23664206249837</v>
       </c>
       <c r="I14" t="n">
-        <v>3.399346217055711</v>
+        <v>1.554206382682917</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722948919299216</v>
+        <v>4.680266336809455</v>
       </c>
       <c r="K14" t="n">
-        <v>15.44675947375706</v>
+        <v>18.66470264630613</v>
       </c>
       <c r="L14" t="n">
-        <v>44.37381621476719</v>
+        <v>42.44407983655076</v>
       </c>
       <c r="M14" t="n">
-        <v>99.88684010733624</v>
+        <v>99.94822609819428</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.99985879779015</v>
+        <v>80.23901896226964</v>
       </c>
       <c r="C15" t="n">
-        <v>40.03870773624883</v>
+        <v>37.95689110717767</v>
       </c>
       <c r="D15" t="n">
-        <v>1.539540024127676</v>
+        <v>1.537399395603966</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4585677657021</v>
+        <v>10.61424211503864</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7565222521470352</v>
+        <v>0.7492538432781785</v>
       </c>
       <c r="G15" t="n">
-        <v>25.32913683128728</v>
+        <v>25.07683990506681</v>
       </c>
       <c r="H15" t="n">
-        <v>36.35185134424611</v>
+        <v>36.25654153387762</v>
       </c>
       <c r="I15" t="n">
-        <v>2.835976504360977</v>
+        <v>1.321905648915801</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728264075918971</v>
+        <v>4.682836520488615</v>
       </c>
       <c r="K15" t="n">
-        <v>16.00014120220986</v>
+        <v>19.76098103773037</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86672477773422</v>
+        <v>42.23808851780859</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9055737161929</v>
+        <v>99.95596066271663</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.8082641276918</v>
+        <v>77.57852195366895</v>
       </c>
       <c r="C16" t="n">
-        <v>38.28605782877146</v>
+        <v>35.50083625718077</v>
       </c>
       <c r="D16" t="n">
-        <v>1.455147100728623</v>
+        <v>1.428206652899331</v>
       </c>
       <c r="E16" t="n">
-        <v>12.16989207987958</v>
+        <v>10.04405776255501</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7572514461050546</v>
+        <v>0.7496086493518973</v>
       </c>
       <c r="G16" t="n">
-        <v>23.94067023031135</v>
+        <v>23.29577446727041</v>
       </c>
       <c r="H16" t="n">
-        <v>36.3868900364826</v>
+        <v>36.27371066989696</v>
       </c>
       <c r="I16" t="n">
-        <v>2.365591696027994</v>
+        <v>1.102109693245974</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732821538156592</v>
+        <v>4.685054058449358</v>
       </c>
       <c r="K16" t="n">
-        <v>18.19173587230818</v>
+        <v>22.42147804633106</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44342917379922</v>
+        <v>42.0409660951294</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92122287487888</v>
+        <v>99.96328039864122</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.49922637348654</v>
+        <v>82.81492858867242</v>
       </c>
       <c r="C17" t="n">
-        <v>39.49383351829422</v>
+        <v>38.96819124062918</v>
       </c>
       <c r="D17" t="n">
-        <v>1.456555006744194</v>
+        <v>1.42891056675607</v>
       </c>
       <c r="E17" t="n">
-        <v>12.9696407375708</v>
+        <v>11.87717187714787</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7579841135211098</v>
+        <v>0.7499781056307481</v>
       </c>
       <c r="G17" t="n">
-        <v>24.34786533387624</v>
+        <v>24.93133677008219</v>
       </c>
       <c r="H17" t="n">
-        <v>36.80612729559826</v>
+        <v>37.91566935036624</v>
       </c>
       <c r="I17" t="n">
-        <v>2.423653176668988</v>
+        <v>1.224498758497113</v>
       </c>
       <c r="J17" t="n">
-        <v>4.737400709506937</v>
+        <v>4.687363160192175</v>
       </c>
       <c r="K17" t="n">
-        <v>16.50077362651348</v>
+        <v>17.18507141132759</v>
       </c>
       <c r="L17" t="n">
-        <v>43.92468250607234</v>
+        <v>43.8059408299583</v>
       </c>
       <c r="M17" t="n">
-        <v>99.91928965088005</v>
+        <v>99.95920348191507</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.41617372956972</v>
+        <v>84.34539471977686</v>
       </c>
       <c r="C18" t="n">
-        <v>37.78561104455513</v>
+        <v>39.70192239267461</v>
       </c>
       <c r="D18" t="n">
-        <v>1.379445411183325</v>
+        <v>1.430026516948647</v>
       </c>
       <c r="E18" t="n">
-        <v>12.61992883429252</v>
+        <v>12.47295651581977</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7586114154996043</v>
+        <v>0.7505638233312666</v>
       </c>
       <c r="G18" t="n">
-        <v>23.05889647243768</v>
+        <v>25.0793819333156</v>
       </c>
       <c r="H18" t="n">
-        <v>36.83658777103751</v>
+        <v>37.94528071968328</v>
       </c>
       <c r="I18" t="n">
-        <v>2.021382478246545</v>
+        <v>1.976161314857871</v>
       </c>
       <c r="J18" t="n">
-        <v>4.741321346872527</v>
+        <v>4.691023895820416</v>
       </c>
       <c r="K18" t="n">
-        <v>18.58382627043028</v>
+        <v>15.65460528022316</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56323898566269</v>
+        <v>44.57765168785888</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9326763006481</v>
+        <v>99.93417936075664</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.59630640427616</v>
+        <v>81.27464498052552</v>
       </c>
       <c r="C19" t="n">
-        <v>37.2777623745427</v>
+        <v>36.93664589944976</v>
       </c>
       <c r="D19" t="n">
-        <v>1.349867347985541</v>
+        <v>1.318269702185771</v>
       </c>
       <c r="E19" t="n">
-        <v>12.6302756616714</v>
+        <v>11.77284520038593</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7591402903292142</v>
+        <v>0.7510711011391702</v>
       </c>
       <c r="G19" t="n">
-        <v>22.56446770301805</v>
+        <v>23.11942398297669</v>
       </c>
       <c r="H19" t="n">
-        <v>36.8622688294592</v>
+        <v>37.970926505192</v>
       </c>
       <c r="I19" t="n">
-        <v>1.685659757255161</v>
+        <v>1.647914106526125</v>
       </c>
       <c r="J19" t="n">
-        <v>4.744626814557589</v>
+        <v>4.694194382119814</v>
       </c>
       <c r="K19" t="n">
-        <v>19.40369359572383</v>
+        <v>18.7253550194745</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26239451644882</v>
+        <v>44.28310571121858</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94385048671535</v>
+        <v>99.94510663014283</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.31408660359881</v>
+        <v>78.21050240332373</v>
       </c>
       <c r="C20" t="n">
-        <v>35.25565061305674</v>
+        <v>34.12634436872555</v>
       </c>
       <c r="D20" t="n">
-        <v>1.266324938674052</v>
+        <v>1.207424159876342</v>
       </c>
       <c r="E20" t="n">
-        <v>12.08285561699103</v>
+        <v>11.01194691694267</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7595944507821375</v>
+        <v>0.7515109488207883</v>
       </c>
       <c r="G20" t="n">
-        <v>21.1679675213116</v>
+        <v>21.17544765929604</v>
       </c>
       <c r="H20" t="n">
-        <v>36.88432191361326</v>
+        <v>37.9931633133542</v>
       </c>
       <c r="I20" t="n">
-        <v>1.405556844838379</v>
+        <v>1.374065974903769</v>
       </c>
       <c r="J20" t="n">
-        <v>4.747465317388359</v>
+        <v>4.696943430129926</v>
       </c>
       <c r="K20" t="n">
-        <v>21.68591339640118</v>
+        <v>21.78949759667626</v>
       </c>
       <c r="L20" t="n">
-        <v>43.01161210839609</v>
+        <v>44.03838264275025</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95317611785401</v>
+        <v>99.95422460815206</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.68882149013066</v>
+        <v>75.14498537933602</v>
       </c>
       <c r="C21" t="n">
-        <v>38.35502942308525</v>
+        <v>31.27165515746256</v>
       </c>
       <c r="D21" t="n">
-        <v>1.267474297239342</v>
+        <v>1.09714450013026</v>
       </c>
       <c r="E21" t="n">
-        <v>13.82425972696604</v>
+        <v>10.19711411021783</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7602838839295788</v>
+        <v>0.7518928588299955</v>
       </c>
       <c r="G21" t="n">
-        <v>22.53782381331309</v>
+        <v>19.2413956165762</v>
       </c>
       <c r="H21" t="n">
-        <v>38.2684428907554</v>
+        <v>38.01247104183584</v>
       </c>
       <c r="I21" t="n">
-        <v>2.278762603367344</v>
+        <v>1.14563688405844</v>
       </c>
       <c r="J21" t="n">
-        <v>4.751774274559867</v>
+        <v>4.699330367687471</v>
       </c>
       <c r="K21" t="n">
-        <v>16.31117850986934</v>
+        <v>24.85501462066396</v>
       </c>
       <c r="L21" t="n">
-        <v>45.25790219376891</v>
+        <v>43.8351617225706</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92411012672349</v>
+        <v>99.96183150069712</v>
       </c>
     </row>
   </sheetData>
